--- a/verification/cases/roundtrip/textbox/init.xlsx
+++ b/verification/cases/roundtrip/textbox/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01D0AD71-D8D7-4A8B-B24C-CEBD6C8B556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="27795" windowHeight="11820"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -65,6 +71,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -86,7 +95,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -179,9 +194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -219,7 +234,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -291,7 +306,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -464,9 +479,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -474,18 +489,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
